--- a/Documentation/ProjectLog-G12-4645-350-1261.xlsx
+++ b/Documentation/ProjectLog-G12-4645-350-1261.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="DP1.0" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="52">
   <si>
     <r>
       <rPr>
@@ -401,10 +401,16 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Gxx</t>
+    <t xml:space="preserve">Remove all unnecessary/nonsensical figures from project report. Prepare complete overhaul of report: almost nothing can be preserved. </t>
   </si>
   <si>
-    <t xml:space="preserve">%</t>
+    <t xml:space="preserve">Create new megasections: design principles, design topologies. Clearly seperate content into sections to minimize overlap.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Write design principles megasection: 2.1: ripple carry, 2.2: carry select, 2.3: overflow detection. Add appropriate figures to highlight reasoning behind propagation delay and cost.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Write design topologies megasection: 3.1 RCAN, 3.2 RCAN. Add VHDL code to outline code structure.</t>
   </si>
   <si>
     <r>
@@ -448,6 +454,12 @@
       </rPr>
       <t xml:space="preserve">(organisation &amp; template reports)</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Gxx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">%</t>
   </si>
   <si>
     <r>
@@ -5332,7 +5344,9 @@
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6"/>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="7" t="s">
@@ -5345,7 +5359,9 @@
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="8"/>
+      <c r="B3" s="8" t="n">
+        <v>301544645</v>
+      </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
       <c r="E3" s="7"/>
@@ -5357,7 +5373,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -5369,11 +5385,11 @@
       <c r="A5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
+      <c r="B5" s="11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
@@ -5431,73 +5447,123 @@
     </row>
     <row r="7" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="19"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="23"/>
+      <c r="B7" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="30" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D7" s="22" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="E7" s="32" t="n">
+        <v>0.666666666666667</v>
+      </c>
       <c r="F7" s="24"/>
-      <c r="G7" s="25"/>
+      <c r="G7" s="25" t="s">
+        <v>42</v>
+      </c>
       <c r="H7" s="26" t="n">
         <f aca="false">(E7-D7)*24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" s="27"/>
     </row>
     <row r="8" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="28"/>
-      <c r="B8" s="29"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="32"/>
+      <c r="B8" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="30" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D8" s="32" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="E8" s="32" t="n">
+        <v>0.75</v>
+      </c>
       <c r="F8" s="33"/>
-      <c r="G8" s="34"/>
+      <c r="G8" s="34" t="s">
+        <v>43</v>
+      </c>
       <c r="H8" s="35" t="n">
         <f aca="false">(E8-D8)*24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="28"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="32"/>
+      <c r="B9" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="30" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D9" s="32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E9" s="32" t="n">
+        <v>0.833333333333333</v>
+      </c>
       <c r="F9" s="33"/>
-      <c r="G9" s="34"/>
+      <c r="G9" s="34" t="s">
+        <v>44</v>
+      </c>
       <c r="H9" s="35" t="n">
         <f aca="false">(E9-D9)*24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="28"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="32"/>
+      <c r="B10" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="30" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D10" s="32" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="E10" s="32" t="n">
+        <v>0.916666666666667</v>
+      </c>
       <c r="F10" s="33"/>
-      <c r="G10" s="34"/>
+      <c r="G10" s="34" t="s">
+        <v>45</v>
+      </c>
       <c r="H10" s="35" t="n">
         <f aca="false">(E10-D10)*24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="28"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="32"/>
+      <c r="B11" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="30" t="n">
+        <v>46081</v>
+      </c>
+      <c r="D11" s="32" t="n">
+        <v>0.916666666666667</v>
+      </c>
+      <c r="E11" s="32" t="n">
+        <v>0.999305555555556</v>
+      </c>
       <c r="F11" s="33"/>
       <c r="G11" s="34"/>
       <c r="H11" s="35" t="n">
         <f aca="false">(E11-D11)*24</f>
-        <v>0</v>
+        <v>1.98333333333333</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="28"/>
-      <c r="B12" s="29"/>
+      <c r="B12" s="20" t="s">
+        <v>15</v>
+      </c>
       <c r="C12" s="30"/>
       <c r="D12" s="22"/>
       <c r="E12" s="32"/>
@@ -5510,7 +5576,9 @@
     </row>
     <row r="13" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="28"/>
-      <c r="B13" s="29"/>
+      <c r="B13" s="29" t="s">
+        <v>15</v>
+      </c>
       <c r="C13" s="30"/>
       <c r="D13" s="22"/>
       <c r="E13" s="32"/>
@@ -5523,7 +5591,9 @@
     </row>
     <row r="14" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="28"/>
-      <c r="B14" s="29"/>
+      <c r="B14" s="29" t="s">
+        <v>15</v>
+      </c>
       <c r="C14" s="30"/>
       <c r="D14" s="22"/>
       <c r="E14" s="32"/>
@@ -5536,7 +5606,9 @@
     </row>
     <row r="15" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="28"/>
-      <c r="B15" s="29"/>
+      <c r="B15" s="29" t="s">
+        <v>15</v>
+      </c>
       <c r="C15" s="30"/>
       <c r="D15" s="22"/>
       <c r="E15" s="32"/>
@@ -5549,7 +5621,9 @@
     </row>
     <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="28"/>
-      <c r="B16" s="29"/>
+      <c r="B16" s="29" t="s">
+        <v>15</v>
+      </c>
       <c r="C16" s="30"/>
       <c r="D16" s="22"/>
       <c r="E16" s="32"/>
@@ -5562,7 +5636,9 @@
     </row>
     <row r="17" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="28"/>
-      <c r="B17" s="29"/>
+      <c r="B17" s="20" t="s">
+        <v>15</v>
+      </c>
       <c r="C17" s="30"/>
       <c r="D17" s="22"/>
       <c r="E17" s="32"/>
@@ -5575,7 +5651,9 @@
     </row>
     <row r="18" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="28"/>
-      <c r="B18" s="29"/>
+      <c r="B18" s="29" t="s">
+        <v>15</v>
+      </c>
       <c r="C18" s="30"/>
       <c r="D18" s="22"/>
       <c r="E18" s="32"/>
@@ -6383,7 +6461,7 @@
       <c r="F80" s="46"/>
       <c r="H80" s="47" t="n">
         <f aca="false">SUM(H7:H79)</f>
-        <v>0</v>
+        <v>9.98333333333333</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -7153,7 +7231,7 @@
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
@@ -7174,7 +7252,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -7187,7 +7265,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -8970,7 +9048,7 @@
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
@@ -8991,7 +9069,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -9004,7 +9082,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -10769,7 +10847,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -10787,7 +10865,7 @@
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="7" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
@@ -10808,7 +10886,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -10821,7 +10899,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>

--- a/Documentation/ProjectLog-G12-4645-350-1261.xlsx
+++ b/Documentation/ProjectLog-G12-4645-350-1261.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="55">
   <si>
     <r>
       <rPr>
@@ -413,6 +413,15 @@
     <t xml:space="preserve">Write design topologies megasection: 3.1 RCAN, 3.2 RCAN. Add VHDL code to outline code structure.</t>
   </si>
   <si>
+    <t xml:space="preserve">Do research on how to accurately make estimates about performance. Idea: use estimates based on theoretical circuit structures, and then verify that quartus does not do any drastic restructuring that completely contradicts the theoretical circuit structure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clean up CSAN, RCAN, code: make them use the same full adder entities. Remove FA.vhd from project. Edit .do scripts to reflect this change. Create new vhdl listing to reflect these changes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add waveform images, RTL images, VHDL code snippets, and expressions for the design topologies megasection, for use in later parts. </t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="26"/>
@@ -588,7 +597,7 @@
     <numFmt numFmtId="169" formatCode="0.00"/>
     <numFmt numFmtId="170" formatCode="h:mm:ss"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -708,6 +717,12 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -916,7 +931,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1108,6 +1123,10 @@
     <xf numFmtId="169" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="true"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="4" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -5553,7 +5572,9 @@
         <v>0.999305555555556</v>
       </c>
       <c r="F11" s="33"/>
-      <c r="G11" s="34"/>
+      <c r="G11" s="34" t="s">
+        <v>46</v>
+      </c>
       <c r="H11" s="35" t="n">
         <f aca="false">(E11-D11)*24</f>
         <v>1.98333333333333</v>
@@ -5564,14 +5585,22 @@
       <c r="B12" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="30"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="32"/>
+      <c r="C12" s="30" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="E12" s="32" t="n">
+        <v>0.666666666666667</v>
+      </c>
       <c r="F12" s="33"/>
-      <c r="G12" s="34"/>
+      <c r="G12" s="48" t="s">
+        <v>47</v>
+      </c>
       <c r="H12" s="35" t="n">
         <f aca="false">(E12-D12)*24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5579,14 +5608,22 @@
       <c r="B13" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="30"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="32"/>
+      <c r="C13" s="30" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D13" s="32" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="E13" s="32" t="n">
+        <v>0.75</v>
+      </c>
       <c r="F13" s="33"/>
-      <c r="G13" s="34"/>
+      <c r="G13" s="34" t="s">
+        <v>48</v>
+      </c>
       <c r="H13" s="35" t="n">
         <f aca="false">(E13-D13)*24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5594,14 +5631,20 @@
       <c r="B14" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="30"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="32"/>
+      <c r="C14" s="30" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D14" s="32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E14" s="32" t="n">
+        <v>0.833333333333333</v>
+      </c>
       <c r="F14" s="33"/>
       <c r="G14" s="34"/>
       <c r="H14" s="35" t="n">
         <f aca="false">(E14-D14)*24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5609,14 +5652,20 @@
       <c r="B15" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="30"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="32"/>
+      <c r="C15" s="30" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D15" s="32" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="E15" s="32" t="n">
+        <v>0.916666666666667</v>
+      </c>
       <c r="F15" s="33"/>
       <c r="G15" s="34"/>
       <c r="H15" s="35" t="n">
         <f aca="false">(E15-D15)*24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5624,14 +5673,20 @@
       <c r="B16" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="30"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="32"/>
+      <c r="C16" s="30" t="n">
+        <v>46082</v>
+      </c>
+      <c r="D16" s="32" t="n">
+        <v>0.916666666666667</v>
+      </c>
+      <c r="E16" s="32" t="n">
+        <v>0.999305555555556</v>
+      </c>
       <c r="F16" s="33"/>
       <c r="G16" s="34"/>
       <c r="H16" s="35" t="n">
         <f aca="false">(E16-D16)*24</f>
-        <v>0</v>
+        <v>1.98333333333333</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6461,7 +6516,7 @@
       <c r="F80" s="46"/>
       <c r="H80" s="47" t="n">
         <f aca="false">SUM(H7:H79)</f>
-        <v>9.98333333333333</v>
+        <v>19.9666666666667</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -7231,7 +7286,7 @@
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
@@ -7252,7 +7307,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -7265,7 +7320,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -9048,7 +9103,7 @@
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
@@ -9069,7 +9124,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -9082,7 +9137,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -10847,7 +10902,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -10865,7 +10920,7 @@
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
@@ -10886,7 +10941,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -10899,7 +10954,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>

--- a/Documentation/ProjectLog-G12-4645-350-1261.xlsx
+++ b/Documentation/ProjectLog-G12-4645-350-1261.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="66">
   <si>
     <r>
       <rPr>
@@ -422,6 +422,39 @@
     <t xml:space="preserve">Add waveform images, RTL images, VHDL code snippets, and expressions for the design topologies megasection, for use in later parts. </t>
   </si>
   <si>
+    <t xml:space="preserve">Clean up introductory segments. Combined Introduction, Background, and Purpose Statement to form Introduction.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Quartus inexplicable LE usage: RCAN with N=21 uses a standard chain with 2*21 + 1 = 43 LEs, but for some reason at N=22 it uses 51 Les?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clean up CSAN VHDL Code: only include necessary bits. Explain Overflow Detection logic in sections 2.1, 2.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create counting expressions for each design topology using the observed structure from the Quartus RTL diagrams alongside theoretical cost derived in section 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Improve sections 3.1, 3.2. Touch on main entities used in each topology. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research FPGA-specific speed metrics. Determined that the Cyclone IV has speed grade 7 meaning ~473MHz, Arria II has speed grade 6 meaning ~500MHz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fully finish inserting TVPF images into the appropriate sections.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acquire resource utilization numbers for the design candidates for different values of N.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create theoretical speedup equation for CSAN and RCAN topologies. Create normalized performance metric equations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create ALM to LE conversion ratio using the average of the theoretical conversion factor and the experimental conversion factor due to their relative similarity. Create normalized cost metric equations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create final cost-performance table, write conclusion. Proofread report one final time.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="26"/>
@@ -597,7 +630,7 @@
     <numFmt numFmtId="169" formatCode="0.00"/>
     <numFmt numFmtId="170" formatCode="h:mm:ss"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -717,12 +750,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -931,7 +958,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="48">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1123,10 +1150,6 @@
     <xf numFmtId="169" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="true"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="4" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -5595,7 +5618,7 @@
         <v>0.666666666666667</v>
       </c>
       <c r="F12" s="33"/>
-      <c r="G12" s="48" t="s">
+      <c r="G12" s="34" t="s">
         <v>47</v>
       </c>
       <c r="H12" s="35" t="n">
@@ -5641,7 +5664,9 @@
         <v>0.833333333333333</v>
       </c>
       <c r="F14" s="33"/>
-      <c r="G14" s="34"/>
+      <c r="G14" s="34" t="s">
+        <v>49</v>
+      </c>
       <c r="H14" s="35" t="n">
         <f aca="false">(E14-D14)*24</f>
         <v>2</v>
@@ -5662,7 +5687,9 @@
         <v>0.916666666666667</v>
       </c>
       <c r="F15" s="33"/>
-      <c r="G15" s="34"/>
+      <c r="G15" s="34" t="s">
+        <v>50</v>
+      </c>
       <c r="H15" s="35" t="n">
         <f aca="false">(E15-D15)*24</f>
         <v>2</v>
@@ -5683,7 +5710,9 @@
         <v>0.999305555555556</v>
       </c>
       <c r="F16" s="33"/>
-      <c r="G16" s="34"/>
+      <c r="G16" s="34" t="s">
+        <v>51</v>
+      </c>
       <c r="H16" s="35" t="n">
         <f aca="false">(E16-D16)*24</f>
         <v>1.98333333333333</v>
@@ -5694,14 +5723,22 @@
       <c r="B17" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="30"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="32"/>
+      <c r="C17" s="30" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D17" s="22" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="E17" s="32" t="n">
+        <v>0.666666666666667</v>
+      </c>
       <c r="F17" s="33"/>
-      <c r="G17" s="34"/>
+      <c r="G17" s="34" t="s">
+        <v>52</v>
+      </c>
       <c r="H17" s="35" t="n">
         <f aca="false">(E17-D17)*24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5709,118 +5746,202 @@
       <c r="B18" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="30"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="32"/>
+      <c r="C18" s="30" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D18" s="32" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="E18" s="32" t="n">
+        <v>0.75</v>
+      </c>
       <c r="F18" s="33"/>
-      <c r="G18" s="34"/>
+      <c r="G18" s="34" t="s">
+        <v>53</v>
+      </c>
       <c r="H18" s="35" t="n">
         <f aca="false">(E18-D18)*24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="28"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="32"/>
+      <c r="B19" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="30" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D19" s="32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E19" s="32" t="n">
+        <v>0.833333333333333</v>
+      </c>
       <c r="F19" s="33"/>
-      <c r="G19" s="34"/>
+      <c r="G19" s="34" t="s">
+        <v>54</v>
+      </c>
       <c r="H19" s="35" t="n">
         <f aca="false">(E19-D19)*24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="28"/>
-      <c r="B20" s="29"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="32"/>
+      <c r="B20" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="30" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D20" s="32" t="n">
+        <v>0.833333333333333</v>
+      </c>
+      <c r="E20" s="32" t="n">
+        <v>0.916666666666667</v>
+      </c>
       <c r="F20" s="33"/>
-      <c r="G20" s="34"/>
+      <c r="G20" s="34" t="s">
+        <v>55</v>
+      </c>
       <c r="H20" s="35" t="n">
         <f aca="false">(E20-D20)*24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="28"/>
-      <c r="B21" s="29"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="32"/>
+      <c r="B21" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="30" t="n">
+        <v>46083</v>
+      </c>
+      <c r="D21" s="32" t="n">
+        <v>0.916666666666667</v>
+      </c>
+      <c r="E21" s="32" t="n">
+        <v>0.999305555555556</v>
+      </c>
       <c r="F21" s="33"/>
-      <c r="G21" s="34"/>
+      <c r="G21" s="34" t="s">
+        <v>56</v>
+      </c>
       <c r="H21" s="35" t="n">
         <f aca="false">(E21-D21)*24</f>
-        <v>0</v>
+        <v>1.98333333333333</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="28"/>
-      <c r="B22" s="29"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="32"/>
+      <c r="B22" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="30" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D22" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="22" t="n">
+        <v>0</v>
+      </c>
       <c r="F22" s="33"/>
-      <c r="G22" s="34"/>
+      <c r="G22" s="34" t="s">
+        <v>57</v>
+      </c>
       <c r="H22" s="35" t="n">
-        <f aca="false">(E22-D22)*24</f>
-        <v>0</v>
+        <f aca="false">(E24-D24)*24</f>
+        <v>2</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="28"/>
-      <c r="B23" s="29"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="32"/>
+      <c r="B23" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="30" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D23" s="22" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="E23" s="32" t="n">
+        <v>0.666666666666667</v>
+      </c>
       <c r="F23" s="33"/>
-      <c r="G23" s="34"/>
+      <c r="G23" s="34" t="s">
+        <v>58</v>
+      </c>
       <c r="H23" s="35" t="n">
-        <f aca="false">(E23-D23)*24</f>
-        <v>0</v>
+        <f aca="false">(E25-D25)*24</f>
+        <v>2</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="28"/>
-      <c r="B24" s="29"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="32"/>
+      <c r="B24" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="30" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D24" s="32" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="E24" s="32" t="n">
+        <v>0.75</v>
+      </c>
       <c r="F24" s="33"/>
-      <c r="G24" s="34"/>
+      <c r="G24" s="34" t="s">
+        <v>59</v>
+      </c>
       <c r="H24" s="35" t="n">
-        <f aca="false">(E24-D24)*24</f>
-        <v>0</v>
+        <f aca="false">(E26-D26)*24</f>
+        <v>2</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="28"/>
-      <c r="B25" s="29"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="32"/>
+      <c r="B25" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="30" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D25" s="32" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="E25" s="32" t="n">
+        <v>0.75</v>
+      </c>
       <c r="F25" s="33"/>
       <c r="G25" s="34"/>
       <c r="H25" s="35" t="n">
         <f aca="false">(E25-D25)*24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="28"/>
-      <c r="B26" s="29"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="32"/>
+      <c r="B26" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="30" t="n">
+        <v>46084</v>
+      </c>
+      <c r="D26" s="32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E26" s="32" t="n">
+        <v>0.833333333333333</v>
+      </c>
       <c r="F26" s="33"/>
       <c r="G26" s="34"/>
       <c r="H26" s="35" t="n">
         <f aca="false">(E26-D26)*24</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6516,7 +6637,7 @@
       <c r="F80" s="46"/>
       <c r="H80" s="47" t="n">
         <f aca="false">SUM(H7:H79)</f>
-        <v>19.9666666666667</v>
+        <v>39.95</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -7286,7 +7407,7 @@
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="7" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
@@ -7307,7 +7428,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -7320,7 +7441,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -9103,7 +9224,7 @@
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="7" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
@@ -9124,7 +9245,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -9137,7 +9258,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -10902,7 +11023,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -10920,7 +11041,7 @@
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="7" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
@@ -10941,7 +11062,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -10954,7 +11075,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
